--- a/docs/StructureDefinition-br-core-healthcareservice.xlsx
+++ b/docs/StructureDefinition-br-core-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T10:02:10-03:00</t>
+    <t>2026-09-25T17:16:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-br-core-healthcareservice.xlsx
+++ b/docs/StructureDefinition-br-core-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T17:16:20-03:00</t>
+    <t>2026-09-28T11:57:19-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
